--- a/reports/集团总公司_利润表_2026-07.xlsx
+++ b/reports/集团总公司_利润表_2026-07.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>252626342</v>
+        <v>275733746</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>191910541</v>
+        <v>208843852</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1167243850</v>
+        <v>1269476527</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>782754</v>
+        <v>1011970</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4859650</v>
+        <v>6289659</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>680072</v>
+        <v>886804</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4216906</v>
+        <v>5502788</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>578164</v>
+        <v>749876</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3575053</v>
+        <v>4644859</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>530658</v>
+        <v>693380</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3288283</v>
+        <v>4287468</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>287717</v>
+        <v>381922</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1786551</v>
+        <v>2358205</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>230903</v>
+        <v>301158</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1429725</v>
+        <v>1858136</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>249536074</v>
+        <v>271708636</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>188820273</v>
+        <v>204818742</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>97458463</v>
+        <v>107218753</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>579286027</v>
+        <v>636639684</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1790133</v>
+        <v>3171199</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>11081062</v>
+        <v>19662976</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1616623</v>
+        <v>2303474</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>10008950</v>
+        <v>14301079</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>86033900</v>
+        <v>90704085</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>535777505</v>
+        <v>564924918</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1845316</v>
+        <v>2296121</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>11436067</v>
+        <v>14299461</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>810270</v>
+        <v>1148714</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>5005732</v>
+        <v>7148587</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2880121</v>
+        <v>3446781</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>17868906</v>
+        <v>21442315</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1265848</v>
+        <v>1725924</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>7860663</v>
+        <v>10720483</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>60533999</v>
+        <v>60581892</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>373969394</v>
+        <v>373703426</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>181802</v>
+        <v>175478</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1223102</v>
+        <v>1225423</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3677836</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>22723924</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2454688</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>15150273</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>187376434</v>
+        <v>212407297</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>151303203</v>
+        <v>160200909</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>119999409</v>
+        <v>129045416</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>720451746</v>
+        <v>771134221</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>31303794</v>
+        <v>31155493</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>193730206</v>
+        <v>193798600</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>6112837</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>37897478</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1952772</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>12127402</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1218808</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>7579310</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1461407</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>9094326</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1095971</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>6819870</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>731127</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4545938</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>610048</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3787795</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3417308</v>
+        <v>3404575</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>21097337</v>
+        <v>21080601</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1602648</v>
+        <v>1602804</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>9935803</v>
+        <v>9932366</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>4133446</v>
+        <v>4171525</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>25718952</v>
+        <v>25729127</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>26943271</v>
+        <v>26992420</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>172126150</v>
+        <v>172131485</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>385937</v>
+        <v>3297525</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2511781</v>
+        <v>20377189</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1193269</v>
+        <v>1157373</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>8051777</v>
+        <v>8074533</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1241798</v>
+        <v>1104834</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>8336220</v>
+        <v>7714286</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>130182</v>
+        <v>123807</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>862355</v>
+        <v>865246</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>491094</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3439747</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>1067701</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6632159</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>326420</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2293373</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>244642</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1719993</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>407747</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2866478</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1523390</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>9470532</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>217919</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1528482</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163716</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1146244</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>273338</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1910253</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>191622</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1337115</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>137007</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>955081</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>109639</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>764101</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>82193</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>573123</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>62159640</v>
+        <v>62929324</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>67400018</v>
+        <v>67295554</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>610996</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3789789</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136158</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>955554</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>226900</v>
+        <v>215536</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1509571</v>
+        <v>1514491</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>61932740</v>
+        <v>63324784</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7632783</v>
+        <v>7282555</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>51000360</v>
+        <v>51200092</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>54299957</v>
+        <v>56042229</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>54299957</v>
+        <v>56042229</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>54299957</v>
+        <v>56042229</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>54299957</v>
+        <v>56042229</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>54299957</v>
+        <v>56042229</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
